--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,6 +1151,1618 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122187226</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>406168</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7062607</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>riktigt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122187210</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>406074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7061954</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122187209</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>406088</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7061950</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122187228</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>405889</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7062449</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122187208</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>406081</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7061939</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122187215</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>405954</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7062701</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122187216</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>405903</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7062652</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122187227</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78639</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>405873</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7062559</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122187211</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>406084</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7061995</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122187213</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>406024</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7062128</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122187218</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>405949</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7061869</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122187225</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57480</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>405849</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7062237</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122187212</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>406102</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7061999</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122187214</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>405985</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7062528</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122187217</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nordböle Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>405915</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7061901</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187226</v>
+        <v>122187210</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>57369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406168</v>
+        <v>406074</v>
       </c>
       <c r="R6" t="n">
-        <v>7062607</v>
+        <v>7061954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187210</v>
+        <v>122187214</v>
       </c>
       <c r="B7" t="n">
         <v>57369</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406074</v>
+        <v>405985</v>
       </c>
       <c r="R7" t="n">
-        <v>7061954</v>
+        <v>7062528</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187209</v>
+        <v>122187213</v>
       </c>
       <c r="B8" t="n">
         <v>57369</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406088</v>
+        <v>406024</v>
       </c>
       <c r="R8" t="n">
-        <v>7061950</v>
+        <v>7062128</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187228</v>
+        <v>122187218</v>
       </c>
       <c r="B9" t="n">
-        <v>78639</v>
+        <v>57369</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,21 +1491,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405889</v>
+        <v>405949</v>
       </c>
       <c r="R9" t="n">
-        <v>7062449</v>
+        <v>7061869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187208</v>
+        <v>122187228</v>
       </c>
       <c r="B10" t="n">
-        <v>57369</v>
+        <v>78639</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406081</v>
+        <v>405889</v>
       </c>
       <c r="R10" t="n">
-        <v>7061939</v>
+        <v>7062449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187215</v>
+        <v>122187226</v>
       </c>
       <c r="B11" t="n">
-        <v>57369</v>
+        <v>78639</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405954</v>
+        <v>406168</v>
       </c>
       <c r="R11" t="n">
-        <v>7062701</v>
+        <v>7062607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1796,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187216</v>
+        <v>122187211</v>
       </c>
       <c r="B12" t="n">
         <v>57369</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405903</v>
+        <v>406084</v>
       </c>
       <c r="R12" t="n">
-        <v>7062652</v>
+        <v>7061995</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187227</v>
+        <v>122187217</v>
       </c>
       <c r="B13" t="n">
-        <v>78639</v>
+        <v>57369</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405873</v>
+        <v>405915</v>
       </c>
       <c r="R13" t="n">
-        <v>7062559</v>
+        <v>7061901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187211</v>
+        <v>122187212</v>
       </c>
       <c r="B14" t="n">
         <v>57369</v>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406084</v>
+        <v>406102</v>
       </c>
       <c r="R14" t="n">
-        <v>7061995</v>
+        <v>7061999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187213</v>
+        <v>122187227</v>
       </c>
       <c r="B15" t="n">
-        <v>57369</v>
+        <v>78639</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2133,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406024</v>
+        <v>405873</v>
       </c>
       <c r="R15" t="n">
-        <v>7062128</v>
+        <v>7062559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187218</v>
+        <v>122187208</v>
       </c>
       <c r="B16" t="n">
         <v>57369</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405949</v>
+        <v>406081</v>
       </c>
       <c r="R16" t="n">
-        <v>7061869</v>
+        <v>7061939</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,10 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187225</v>
+        <v>122187209</v>
       </c>
       <c r="B17" t="n">
-        <v>57480</v>
+        <v>57369</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,20 +2343,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2364,29 +2364,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405849</v>
+        <v>406088</v>
       </c>
       <c r="R17" t="n">
-        <v>7062237</v>
+        <v>7061950</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,6 +2407,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,7 +2438,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187212</v>
+        <v>122187215</v>
       </c>
       <c r="B18" t="n">
         <v>57369</v>
@@ -2485,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406102</v>
+        <v>405954</v>
       </c>
       <c r="R18" t="n">
-        <v>7061999</v>
+        <v>7062701</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,10 +2545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187214</v>
+        <v>122187225</v>
       </c>
       <c r="B19" t="n">
-        <v>57369</v>
+        <v>57480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,20 +2557,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2585,17 +2578,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405985</v>
+        <v>405849</v>
       </c>
       <c r="R19" t="n">
-        <v>7062528</v>
+        <v>7062237</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,11 +2633,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,7 +2659,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187217</v>
+        <v>122187216</v>
       </c>
       <c r="B20" t="n">
         <v>57369</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405915</v>
+        <v>405903</v>
       </c>
       <c r="R20" t="n">
-        <v>7061901</v>
+        <v>7062652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187210</v>
+        <v>122187225</v>
       </c>
       <c r="B6" t="n">
-        <v>57369</v>
+        <v>57483</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,20 +1166,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1187,17 +1187,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406074</v>
+        <v>405849</v>
       </c>
       <c r="R6" t="n">
-        <v>7061954</v>
+        <v>7062237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,11 +1242,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187214</v>
+        <v>122187209</v>
       </c>
       <c r="B7" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405985</v>
+        <v>406088</v>
       </c>
       <c r="R7" t="n">
-        <v>7062528</v>
+        <v>7061950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1348,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187213</v>
+        <v>122187214</v>
       </c>
       <c r="B8" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406024</v>
+        <v>405985</v>
       </c>
       <c r="R8" t="n">
-        <v>7062128</v>
+        <v>7062528</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187218</v>
+        <v>122187228</v>
       </c>
       <c r="B9" t="n">
-        <v>57369</v>
+        <v>78643</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1515,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405949</v>
+        <v>405889</v>
       </c>
       <c r="R9" t="n">
-        <v>7061869</v>
+        <v>7062449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1562,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187228</v>
+        <v>122187212</v>
       </c>
       <c r="B10" t="n">
-        <v>78639</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,21 +1605,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405889</v>
+        <v>406102</v>
       </c>
       <c r="R10" t="n">
-        <v>7062449</v>
+        <v>7061999</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1669,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187226</v>
+        <v>122187213</v>
       </c>
       <c r="B11" t="n">
-        <v>78639</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,21 +1712,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406168</v>
+        <v>406024</v>
       </c>
       <c r="R11" t="n">
-        <v>7062607</v>
+        <v>7062128</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1776,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,7 +1806,7 @@
         <v>122187211</v>
       </c>
       <c r="B12" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,7 +1913,7 @@
         <v>122187217</v>
       </c>
       <c r="B13" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2010,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187212</v>
+        <v>122187215</v>
       </c>
       <c r="B14" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406102</v>
+        <v>405954</v>
       </c>
       <c r="R14" t="n">
-        <v>7061999</v>
+        <v>7062701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187227</v>
+        <v>122187218</v>
       </c>
       <c r="B15" t="n">
-        <v>78639</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405873</v>
+        <v>405949</v>
       </c>
       <c r="R15" t="n">
-        <v>7062559</v>
+        <v>7061869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2204,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187208</v>
+        <v>122187226</v>
       </c>
       <c r="B16" t="n">
-        <v>57369</v>
+        <v>78643</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406081</v>
+        <v>406168</v>
       </c>
       <c r="R16" t="n">
-        <v>7061939</v>
+        <v>7062607</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187209</v>
+        <v>122187216</v>
       </c>
       <c r="B17" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406088</v>
+        <v>405903</v>
       </c>
       <c r="R17" t="n">
-        <v>7061950</v>
+        <v>7062652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187215</v>
+        <v>122187208</v>
       </c>
       <c r="B18" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405954</v>
+        <v>406081</v>
       </c>
       <c r="R18" t="n">
-        <v>7062701</v>
+        <v>7061939</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187225</v>
+        <v>122187227</v>
       </c>
       <c r="B19" t="n">
-        <v>57480</v>
+        <v>78643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2557,50 +2564,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405849</v>
+        <v>405873</v>
       </c>
       <c r="R19" t="n">
-        <v>7062237</v>
+        <v>7062559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,6 +2628,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187216</v>
+        <v>122187210</v>
       </c>
       <c r="B20" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405903</v>
+        <v>406074</v>
       </c>
       <c r="R20" t="n">
-        <v>7062652</v>
+        <v>7061954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187225</v>
+        <v>122187209</v>
       </c>
       <c r="B6" t="n">
-        <v>57483</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,20 +1166,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1187,29 +1187,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405849</v>
+        <v>406088</v>
       </c>
       <c r="R6" t="n">
-        <v>7062237</v>
+        <v>7061950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,6 +1230,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187209</v>
+        <v>122187218</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406088</v>
+        <v>405949</v>
       </c>
       <c r="R7" t="n">
-        <v>7061950</v>
+        <v>7061869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187214</v>
+        <v>122187228</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405985</v>
+        <v>405889</v>
       </c>
       <c r="R8" t="n">
-        <v>7062528</v>
+        <v>7062449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187228</v>
+        <v>122187215</v>
       </c>
       <c r="B9" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1491,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405889</v>
+        <v>405954</v>
       </c>
       <c r="R9" t="n">
-        <v>7062449</v>
+        <v>7062701</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187212</v>
+        <v>122187211</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406102</v>
+        <v>406084</v>
       </c>
       <c r="R10" t="n">
-        <v>7061999</v>
+        <v>7061995</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1662,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187213</v>
+        <v>122187214</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406024</v>
+        <v>405985</v>
       </c>
       <c r="R11" t="n">
-        <v>7062128</v>
+        <v>7062528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187211</v>
+        <v>122187212</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406084</v>
+        <v>406102</v>
       </c>
       <c r="R12" t="n">
-        <v>7061995</v>
+        <v>7061999</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1876,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187217</v>
+        <v>122187225</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>57485</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,20 +1915,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1943,17 +1936,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405915</v>
+        <v>405849</v>
       </c>
       <c r="R13" t="n">
-        <v>7061901</v>
+        <v>7062237</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,11 +1991,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187215</v>
+        <v>122187208</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405954</v>
+        <v>406081</v>
       </c>
       <c r="R14" t="n">
-        <v>7062701</v>
+        <v>7061939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187218</v>
+        <v>122187210</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405949</v>
+        <v>406074</v>
       </c>
       <c r="R15" t="n">
-        <v>7061869</v>
+        <v>7061954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187226</v>
+        <v>122187217</v>
       </c>
       <c r="B16" t="n">
-        <v>78643</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406168</v>
+        <v>405915</v>
       </c>
       <c r="R16" t="n">
-        <v>7062607</v>
+        <v>7061901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,7 +2341,7 @@
         <v>122187216</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187208</v>
+        <v>122187227</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>78645</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406081</v>
+        <v>405873</v>
       </c>
       <c r="R18" t="n">
-        <v>7061939</v>
+        <v>7062559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187227</v>
+        <v>122187226</v>
       </c>
       <c r="B19" t="n">
-        <v>78643</v>
+        <v>78645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405873</v>
+        <v>406168</v>
       </c>
       <c r="R19" t="n">
-        <v>7062559</v>
+        <v>7062607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187210</v>
+        <v>122187213</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406074</v>
+        <v>406024</v>
       </c>
       <c r="R20" t="n">
-        <v>7061954</v>
+        <v>7062128</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187209</v>
+        <v>122187226</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406088</v>
+        <v>406168</v>
       </c>
       <c r="R6" t="n">
-        <v>7061950</v>
+        <v>7062607</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187218</v>
+        <v>122187216</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405949</v>
+        <v>405903</v>
       </c>
       <c r="R7" t="n">
-        <v>7061869</v>
+        <v>7062652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187228</v>
+        <v>122187209</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405889</v>
+        <v>406088</v>
       </c>
       <c r="R8" t="n">
-        <v>7062449</v>
+        <v>7061950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187215</v>
+        <v>122187227</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,21 +1491,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405954</v>
+        <v>405873</v>
       </c>
       <c r="R9" t="n">
-        <v>7062701</v>
+        <v>7062559</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,7 +1582,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187211</v>
+        <v>122187208</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406084</v>
+        <v>406081</v>
       </c>
       <c r="R10" t="n">
-        <v>7061995</v>
+        <v>7061939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187214</v>
+        <v>122187225</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>57485</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,20 +1701,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1722,17 +1722,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405985</v>
+        <v>405849</v>
       </c>
       <c r="R11" t="n">
-        <v>7062528</v>
+        <v>7062237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,11 +1777,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1803,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187212</v>
+        <v>122187214</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1836,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406102</v>
+        <v>405985</v>
       </c>
       <c r="R12" t="n">
-        <v>7061999</v>
+        <v>7062528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1883,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187225</v>
+        <v>122187228</v>
       </c>
       <c r="B13" t="n">
-        <v>57485</v>
+        <v>78645</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,50 +1922,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405849</v>
+        <v>405889</v>
       </c>
       <c r="R13" t="n">
-        <v>7062237</v>
+        <v>7062449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,6 +1986,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187208</v>
+        <v>122187213</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406081</v>
+        <v>406024</v>
       </c>
       <c r="R14" t="n">
-        <v>7061939</v>
+        <v>7062128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187210</v>
+        <v>122187212</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406074</v>
+        <v>406102</v>
       </c>
       <c r="R15" t="n">
-        <v>7061954</v>
+        <v>7061999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,7 +2231,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187217</v>
+        <v>122187210</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405915</v>
+        <v>406074</v>
       </c>
       <c r="R16" t="n">
-        <v>7061901</v>
+        <v>7061954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2338,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187216</v>
+        <v>122187217</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405903</v>
+        <v>405915</v>
       </c>
       <c r="R17" t="n">
-        <v>7062652</v>
+        <v>7061901</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187227</v>
+        <v>122187215</v>
       </c>
       <c r="B18" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405873</v>
+        <v>405954</v>
       </c>
       <c r="R18" t="n">
-        <v>7062559</v>
+        <v>7062701</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187226</v>
+        <v>122187211</v>
       </c>
       <c r="B19" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406168</v>
+        <v>406084</v>
       </c>
       <c r="R19" t="n">
-        <v>7062607</v>
+        <v>7061995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,7 +2659,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187213</v>
+        <v>122187218</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406024</v>
+        <v>405949</v>
       </c>
       <c r="R20" t="n">
-        <v>7062128</v>
+        <v>7061869</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187215</v>
+        <v>122187227</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405954</v>
+        <v>405873</v>
       </c>
       <c r="R6" t="n">
-        <v>7062701</v>
+        <v>7062559</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187214</v>
+        <v>122187209</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405985</v>
+        <v>406088</v>
       </c>
       <c r="R7" t="n">
-        <v>7062528</v>
+        <v>7061950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187227</v>
+        <v>122187226</v>
       </c>
       <c r="B8" t="n">
         <v>78645</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405873</v>
+        <v>406168</v>
       </c>
       <c r="R8" t="n">
-        <v>7062559</v>
+        <v>7062607</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187208</v>
+        <v>122187213</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406081</v>
+        <v>406024</v>
       </c>
       <c r="R9" t="n">
-        <v>7061939</v>
+        <v>7062128</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,7 +1582,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187210</v>
+        <v>122187216</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406074</v>
+        <v>405903</v>
       </c>
       <c r="R10" t="n">
-        <v>7061954</v>
+        <v>7062652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,7 +1689,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187216</v>
+        <v>122187217</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405903</v>
+        <v>405915</v>
       </c>
       <c r="R11" t="n">
-        <v>7062652</v>
+        <v>7061901</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1796,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187212</v>
+        <v>122187215</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406102</v>
+        <v>405954</v>
       </c>
       <c r="R12" t="n">
-        <v>7061999</v>
+        <v>7062701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187228</v>
+        <v>122187214</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405889</v>
+        <v>405985</v>
       </c>
       <c r="R13" t="n">
-        <v>7062449</v>
+        <v>7062528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187213</v>
+        <v>122187225</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57485</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2043,17 +2043,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406024</v>
+        <v>405849</v>
       </c>
       <c r="R14" t="n">
-        <v>7062128</v>
+        <v>7062237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,11 +2098,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187226</v>
+        <v>122187208</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,21 +2140,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2157,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406168</v>
+        <v>406081</v>
       </c>
       <c r="R15" t="n">
-        <v>7062607</v>
+        <v>7061939</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2204,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187209</v>
+        <v>122187228</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>78645</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406088</v>
+        <v>405889</v>
       </c>
       <c r="R17" t="n">
-        <v>7061950</v>
+        <v>7062449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2438,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187217</v>
+        <v>122187212</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2478,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405915</v>
+        <v>406102</v>
       </c>
       <c r="R18" t="n">
-        <v>7061901</v>
+        <v>7061999</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2518,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187225</v>
+        <v>122187211</v>
       </c>
       <c r="B19" t="n">
-        <v>57485</v>
+        <v>57374</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2557,20 +2564,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2578,29 +2585,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405849</v>
+        <v>406084</v>
       </c>
       <c r="R19" t="n">
-        <v>7062237</v>
+        <v>7061995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,6 +2628,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,7 +2659,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187211</v>
+        <v>122187210</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406084</v>
+        <v>406074</v>
       </c>
       <c r="R20" t="n">
-        <v>7061995</v>
+        <v>7061954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187227</v>
+        <v>122187215</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405873</v>
+        <v>405954</v>
       </c>
       <c r="R6" t="n">
-        <v>7062559</v>
+        <v>7062701</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187209</v>
+        <v>122187225</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57485</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,20 +1273,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1294,17 +1294,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406088</v>
+        <v>405849</v>
       </c>
       <c r="R7" t="n">
-        <v>7061950</v>
+        <v>7062237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,11 +1349,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187226</v>
+        <v>122187209</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1391,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406168</v>
+        <v>406088</v>
       </c>
       <c r="R8" t="n">
-        <v>7062607</v>
+        <v>7061950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1455,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1482,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187213</v>
+        <v>122187218</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1515,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406024</v>
+        <v>405949</v>
       </c>
       <c r="R9" t="n">
-        <v>7062128</v>
+        <v>7061869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1562,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187216</v>
+        <v>122187227</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,21 +1605,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405903</v>
+        <v>405873</v>
       </c>
       <c r="R10" t="n">
-        <v>7062652</v>
+        <v>7062559</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1669,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187217</v>
+        <v>122187208</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1729,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405915</v>
+        <v>406081</v>
       </c>
       <c r="R11" t="n">
-        <v>7061901</v>
+        <v>7061939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1776,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1803,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187215</v>
+        <v>122187214</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1836,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405954</v>
+        <v>405985</v>
       </c>
       <c r="R12" t="n">
-        <v>7062701</v>
+        <v>7062528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1883,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187214</v>
+        <v>122187217</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1943,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405985</v>
+        <v>405915</v>
       </c>
       <c r="R13" t="n">
-        <v>7062528</v>
+        <v>7061901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1990,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187225</v>
+        <v>122187213</v>
       </c>
       <c r="B14" t="n">
-        <v>57485</v>
+        <v>57374</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,20 +2029,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2043,29 +2050,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405849</v>
+        <v>406024</v>
       </c>
       <c r="R14" t="n">
-        <v>7062237</v>
+        <v>7062128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,6 +2093,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187208</v>
+        <v>122187212</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406081</v>
+        <v>406102</v>
       </c>
       <c r="R15" t="n">
-        <v>7061939</v>
+        <v>7061999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187218</v>
+        <v>122187226</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405949</v>
+        <v>406168</v>
       </c>
       <c r="R16" t="n">
-        <v>7061869</v>
+        <v>7062607</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187228</v>
+        <v>122187216</v>
       </c>
       <c r="B17" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405889</v>
+        <v>405903</v>
       </c>
       <c r="R17" t="n">
-        <v>7062449</v>
+        <v>7062652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187212</v>
+        <v>122187211</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406102</v>
+        <v>406084</v>
       </c>
       <c r="R18" t="n">
-        <v>7061999</v>
+        <v>7061995</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,7 +2552,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187211</v>
+        <v>122187210</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406084</v>
+        <v>406074</v>
       </c>
       <c r="R19" t="n">
-        <v>7061995</v>
+        <v>7061954</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187210</v>
+        <v>122187228</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406074</v>
+        <v>405889</v>
       </c>
       <c r="R20" t="n">
-        <v>7061954</v>
+        <v>7062449</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187215</v>
+        <v>122187228</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405954</v>
+        <v>405889</v>
       </c>
       <c r="R6" t="n">
-        <v>7062701</v>
+        <v>7062449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187225</v>
+        <v>122187215</v>
       </c>
       <c r="B7" t="n">
-        <v>57485</v>
+        <v>57374</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,20 +1273,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1294,29 +1294,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405849</v>
+        <v>405954</v>
       </c>
       <c r="R7" t="n">
-        <v>7062237</v>
+        <v>7062701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,6 +1337,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187209</v>
+        <v>122187211</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1415,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406088</v>
+        <v>406084</v>
       </c>
       <c r="R8" t="n">
-        <v>7061950</v>
+        <v>7061995</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187218</v>
+        <v>122187216</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1522,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405949</v>
+        <v>405903</v>
       </c>
       <c r="R9" t="n">
-        <v>7061869</v>
+        <v>7062652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187227</v>
+        <v>122187217</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,21 +1598,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405873</v>
+        <v>405915</v>
       </c>
       <c r="R10" t="n">
-        <v>7062559</v>
+        <v>7061901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1662,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187208</v>
+        <v>122187225</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>57485</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,20 +1701,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1729,17 +1722,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406081</v>
+        <v>405849</v>
       </c>
       <c r="R11" t="n">
-        <v>7061939</v>
+        <v>7062237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,11 +1777,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187214</v>
+        <v>122187210</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405985</v>
+        <v>406074</v>
       </c>
       <c r="R12" t="n">
-        <v>7062528</v>
+        <v>7061954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187217</v>
+        <v>122187208</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405915</v>
+        <v>406081</v>
       </c>
       <c r="R13" t="n">
-        <v>7061901</v>
+        <v>7061939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187213</v>
+        <v>122187212</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406024</v>
+        <v>406102</v>
       </c>
       <c r="R14" t="n">
-        <v>7062128</v>
+        <v>7061999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187212</v>
+        <v>122187209</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406102</v>
+        <v>406088</v>
       </c>
       <c r="R15" t="n">
-        <v>7061999</v>
+        <v>7061950</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187226</v>
+        <v>122187214</v>
       </c>
       <c r="B16" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406168</v>
+        <v>405985</v>
       </c>
       <c r="R16" t="n">
-        <v>7062607</v>
+        <v>7062528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2338,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187216</v>
+        <v>122187213</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405903</v>
+        <v>406024</v>
       </c>
       <c r="R17" t="n">
-        <v>7062652</v>
+        <v>7062128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187211</v>
+        <v>122187226</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406084</v>
+        <v>406168</v>
       </c>
       <c r="R18" t="n">
-        <v>7061995</v>
+        <v>7062607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187210</v>
+        <v>122187227</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406074</v>
+        <v>405873</v>
       </c>
       <c r="R19" t="n">
-        <v>7061954</v>
+        <v>7062559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187228</v>
+        <v>122187218</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405889</v>
+        <v>405949</v>
       </c>
       <c r="R20" t="n">
-        <v>7062449</v>
+        <v>7061869</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187228</v>
+        <v>122187218</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405889</v>
+        <v>405949</v>
       </c>
       <c r="R6" t="n">
-        <v>7062449</v>
+        <v>7061869</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1264,7 @@
         <v>122187215</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187211</v>
+        <v>122187212</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406084</v>
+        <v>406102</v>
       </c>
       <c r="R8" t="n">
-        <v>7061995</v>
+        <v>7061999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187216</v>
+        <v>122187209</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405903</v>
+        <v>406088</v>
       </c>
       <c r="R9" t="n">
-        <v>7062652</v>
+        <v>7061950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187217</v>
+        <v>122187210</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405915</v>
+        <v>406074</v>
       </c>
       <c r="R10" t="n">
-        <v>7061901</v>
+        <v>7061954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187225</v>
+        <v>122187211</v>
       </c>
       <c r="B11" t="n">
-        <v>57485</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,20 +1701,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1722,29 +1722,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405849</v>
+        <v>406084</v>
       </c>
       <c r="R11" t="n">
-        <v>7062237</v>
+        <v>7061995</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,6 +1765,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187210</v>
+        <v>122187213</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406074</v>
+        <v>406024</v>
       </c>
       <c r="R12" t="n">
-        <v>7061954</v>
+        <v>7062128</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187208</v>
+        <v>122187226</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1950,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406081</v>
+        <v>406168</v>
       </c>
       <c r="R13" t="n">
-        <v>7061939</v>
+        <v>7062607</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1983,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187212</v>
+        <v>122187228</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,21 +2026,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406102</v>
+        <v>405889</v>
       </c>
       <c r="R14" t="n">
-        <v>7061999</v>
+        <v>7062449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2090,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187209</v>
+        <v>122187225</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>57490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,20 +2129,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2157,17 +2150,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406088</v>
+        <v>405849</v>
       </c>
       <c r="R15" t="n">
-        <v>7061950</v>
+        <v>7062237</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,11 +2205,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187214</v>
+        <v>122187227</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>78651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405985</v>
+        <v>405873</v>
       </c>
       <c r="R16" t="n">
-        <v>7062528</v>
+        <v>7062559</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187213</v>
+        <v>122187217</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406024</v>
+        <v>405915</v>
       </c>
       <c r="R17" t="n">
-        <v>7062128</v>
+        <v>7061901</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187226</v>
+        <v>122187216</v>
       </c>
       <c r="B18" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406168</v>
+        <v>405903</v>
       </c>
       <c r="R18" t="n">
-        <v>7062607</v>
+        <v>7062652</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187227</v>
+        <v>122187214</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405873</v>
+        <v>405985</v>
       </c>
       <c r="R19" t="n">
-        <v>7062559</v>
+        <v>7062528</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187218</v>
+        <v>122187208</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405949</v>
+        <v>406081</v>
       </c>
       <c r="R20" t="n">
-        <v>7061869</v>
+        <v>7061939</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,7 +1154,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187218</v>
+        <v>122187217</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405949</v>
+        <v>405915</v>
       </c>
       <c r="R6" t="n">
-        <v>7061869</v>
+        <v>7061901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187215</v>
+        <v>122187228</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405954</v>
+        <v>405889</v>
       </c>
       <c r="R7" t="n">
-        <v>7062701</v>
+        <v>7062449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187212</v>
+        <v>122187208</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406102</v>
+        <v>406081</v>
       </c>
       <c r="R8" t="n">
-        <v>7061999</v>
+        <v>7061939</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187209</v>
+        <v>122187216</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406088</v>
+        <v>405903</v>
       </c>
       <c r="R9" t="n">
-        <v>7061950</v>
+        <v>7062652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,7 +1582,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187210</v>
+        <v>122187213</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406074</v>
+        <v>406024</v>
       </c>
       <c r="R10" t="n">
-        <v>7061954</v>
+        <v>7062128</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187211</v>
+        <v>122187209</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406084</v>
+        <v>406088</v>
       </c>
       <c r="R11" t="n">
-        <v>7061995</v>
+        <v>7061950</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1796,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187213</v>
+        <v>122187218</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406024</v>
+        <v>405949</v>
       </c>
       <c r="R12" t="n">
-        <v>7062128</v>
+        <v>7061869</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187226</v>
+        <v>122187214</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406168</v>
+        <v>405985</v>
       </c>
       <c r="R13" t="n">
-        <v>7062607</v>
+        <v>7062528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187228</v>
+        <v>122187211</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405889</v>
+        <v>406084</v>
       </c>
       <c r="R14" t="n">
-        <v>7062449</v>
+        <v>7061995</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187225</v>
+        <v>122187212</v>
       </c>
       <c r="B15" t="n">
-        <v>57490</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,20 +2129,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2150,29 +2150,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405849</v>
+        <v>406102</v>
       </c>
       <c r="R15" t="n">
-        <v>7062237</v>
+        <v>7061999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,6 +2193,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187227</v>
+        <v>122187226</v>
       </c>
       <c r="B16" t="n">
         <v>78651</v>
@@ -2271,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405873</v>
+        <v>406168</v>
       </c>
       <c r="R16" t="n">
-        <v>7062559</v>
+        <v>7062607</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2304,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187217</v>
+        <v>122187225</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2350,20 +2343,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2371,17 +2364,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405915</v>
+        <v>405849</v>
       </c>
       <c r="R17" t="n">
-        <v>7061901</v>
+        <v>7062237</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,11 +2419,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187216</v>
+        <v>122187215</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405903</v>
+        <v>405954</v>
       </c>
       <c r="R18" t="n">
-        <v>7062652</v>
+        <v>7062701</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187214</v>
+        <v>122187227</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405985</v>
+        <v>405873</v>
       </c>
       <c r="R19" t="n">
-        <v>7062528</v>
+        <v>7062559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,7 +2659,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187208</v>
+        <v>122187210</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406081</v>
+        <v>406074</v>
       </c>
       <c r="R20" t="n">
-        <v>7061939</v>
+        <v>7061954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187211</v>
+        <v>122187226</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406084</v>
+        <v>406168</v>
       </c>
       <c r="R14" t="n">
-        <v>7061995</v>
+        <v>7062607</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187212</v>
+        <v>122187211</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406102</v>
+        <v>406084</v>
       </c>
       <c r="R15" t="n">
-        <v>7061999</v>
+        <v>7061995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187226</v>
+        <v>122187212</v>
       </c>
       <c r="B16" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406168</v>
+        <v>406102</v>
       </c>
       <c r="R16" t="n">
-        <v>7062607</v>
+        <v>7061999</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,7 +1154,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187217</v>
+        <v>122187214</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1172,11 +1172,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1194,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405915</v>
+        <v>405985</v>
       </c>
       <c r="R6" t="n">
-        <v>7061901</v>
+        <v>7062528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1229,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187228</v>
+        <v>122187212</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,21 +1272,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405889</v>
+        <v>406102</v>
       </c>
       <c r="R7" t="n">
-        <v>7062449</v>
+        <v>7061999</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1331,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187208</v>
+        <v>122187227</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1374,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406081</v>
+        <v>405873</v>
       </c>
       <c r="R8" t="n">
-        <v>7061939</v>
+        <v>7062559</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1433,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187216</v>
+        <v>122187211</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1493,11 +1478,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1515,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405903</v>
+        <v>406084</v>
       </c>
       <c r="R9" t="n">
-        <v>7062652</v>
+        <v>7061995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1535,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187213</v>
+        <v>122187209</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1600,11 +1580,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1622,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406024</v>
+        <v>406088</v>
       </c>
       <c r="R10" t="n">
-        <v>7062128</v>
+        <v>7061950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1637,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187209</v>
+        <v>122187210</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1707,11 +1682,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1729,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406088</v>
+        <v>406074</v>
       </c>
       <c r="R11" t="n">
-        <v>7061950</v>
+        <v>7061954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1766,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187218</v>
+        <v>122187208</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1814,11 +1784,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1836,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405949</v>
+        <v>406081</v>
       </c>
       <c r="R12" t="n">
-        <v>7061869</v>
+        <v>7061939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1841,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187214</v>
+        <v>122187228</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,21 +1884,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405985</v>
+        <v>405889</v>
       </c>
       <c r="R13" t="n">
-        <v>7062528</v>
+        <v>7062449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1943,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187226</v>
+        <v>122187215</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,21 +1986,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2050,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406168</v>
+        <v>405954</v>
       </c>
       <c r="R14" t="n">
-        <v>7062607</v>
+        <v>7062701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,7 +2045,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2072,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187211</v>
+        <v>122187217</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2135,11 +2090,6 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2157,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406084</v>
+        <v>405915</v>
       </c>
       <c r="R15" t="n">
-        <v>7061995</v>
+        <v>7061901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2147,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187212</v>
+        <v>122187226</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2190,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406102</v>
+        <v>406168</v>
       </c>
       <c r="R16" t="n">
-        <v>7061999</v>
+        <v>7062607</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2249,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187225</v>
+        <v>122187218</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,20 +2288,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2364,29 +2304,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405849</v>
+        <v>405949</v>
       </c>
       <c r="R17" t="n">
-        <v>7062237</v>
+        <v>7061869</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,6 +2347,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,7 +2378,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187215</v>
+        <v>122187213</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2463,11 +2396,6 @@
       <c r="E18" t="n">
         <v>100109</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2485,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405954</v>
+        <v>406024</v>
       </c>
       <c r="R18" t="n">
-        <v>7062701</v>
+        <v>7062128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2453,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187227</v>
+        <v>122187216</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2496,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405873</v>
+        <v>405903</v>
       </c>
       <c r="R19" t="n">
-        <v>7062559</v>
+        <v>7062652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2555,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,10 +2582,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187210</v>
+        <v>122187225</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>57490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,20 +2594,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103031</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2692,17 +2610,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406074</v>
+        <v>405849</v>
       </c>
       <c r="R20" t="n">
-        <v>7061954</v>
+        <v>7062237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,11 +2665,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187214</v>
+        <v>122187209</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,6 +1172,11 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1189,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405985</v>
+        <v>406088</v>
       </c>
       <c r="R6" t="n">
-        <v>7062528</v>
+        <v>7061950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187212</v>
+        <v>122187215</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,6 +1279,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1291,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406102</v>
+        <v>405954</v>
       </c>
       <c r="R7" t="n">
-        <v>7061999</v>
+        <v>7062701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187227</v>
+        <v>122187225</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,33 +1380,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405873</v>
+        <v>405849</v>
       </c>
       <c r="R8" t="n">
-        <v>7062559</v>
+        <v>7062237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,11 +1456,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187211</v>
+        <v>122187227</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,16 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406084</v>
+        <v>405873</v>
       </c>
       <c r="R9" t="n">
-        <v>7061995</v>
+        <v>7062559</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1562,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187209</v>
+        <v>122187212</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,6 +1607,11 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1597,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406088</v>
+        <v>406102</v>
       </c>
       <c r="R10" t="n">
-        <v>7061950</v>
+        <v>7061999</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1669,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187210</v>
+        <v>122187208</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,6 +1714,11 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1699,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406074</v>
+        <v>406081</v>
       </c>
       <c r="R11" t="n">
-        <v>7061954</v>
+        <v>7061939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1776,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187208</v>
+        <v>122187211</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,6 +1821,11 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1801,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406081</v>
+        <v>406084</v>
       </c>
       <c r="R12" t="n">
-        <v>7061939</v>
+        <v>7061995</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1883,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187228</v>
+        <v>122187226</v>
       </c>
       <c r="B13" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,6 +1928,11 @@
       <c r="E13" t="n">
         <v>6425</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1903,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405889</v>
+        <v>406168</v>
       </c>
       <c r="R13" t="n">
-        <v>7062449</v>
+        <v>7062607</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1990,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187215</v>
+        <v>122187213</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,6 +2035,11 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2005,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405954</v>
+        <v>406024</v>
       </c>
       <c r="R14" t="n">
-        <v>7062701</v>
+        <v>7062128</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,7 +2097,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187217</v>
+        <v>122187214</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,6 +2142,11 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2107,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405915</v>
+        <v>405985</v>
       </c>
       <c r="R15" t="n">
-        <v>7061901</v>
+        <v>7062528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,7 +2204,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187226</v>
+        <v>122187210</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,16 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406168</v>
+        <v>406074</v>
       </c>
       <c r="R16" t="n">
-        <v>7062607</v>
+        <v>7061954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187218</v>
+        <v>122187216</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,6 +2356,11 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2311,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405949</v>
+        <v>405903</v>
       </c>
       <c r="R17" t="n">
-        <v>7061869</v>
+        <v>7062652</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2351,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187213</v>
+        <v>122187228</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,16 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406024</v>
+        <v>405889</v>
       </c>
       <c r="R18" t="n">
-        <v>7062128</v>
+        <v>7062449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187216</v>
+        <v>122187217</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,6 +2570,11 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2515,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405903</v>
+        <v>405915</v>
       </c>
       <c r="R19" t="n">
-        <v>7062652</v>
+        <v>7061901</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2582,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187225</v>
+        <v>122187218</v>
       </c>
       <c r="B20" t="n">
-        <v>57490</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2594,15 +2671,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2610,29 +2692,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405849</v>
+        <v>405949</v>
       </c>
       <c r="R20" t="n">
-        <v>7062237</v>
+        <v>7061869</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,6 +2735,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,7 +1154,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187209</v>
+        <v>122187214</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406088</v>
+        <v>405985</v>
       </c>
       <c r="R6" t="n">
-        <v>7061950</v>
+        <v>7062528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187215</v>
+        <v>122187218</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405954</v>
+        <v>405949</v>
       </c>
       <c r="R7" t="n">
-        <v>7062701</v>
+        <v>7061869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187225</v>
+        <v>122187208</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,20 +1380,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1401,29 +1401,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405849</v>
+        <v>406081</v>
       </c>
       <c r="R8" t="n">
-        <v>7062237</v>
+        <v>7061939</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,6 +1444,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187227</v>
+        <v>122187213</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1491,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405873</v>
+        <v>406024</v>
       </c>
       <c r="R9" t="n">
-        <v>7062559</v>
+        <v>7062128</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1555,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,7 +1582,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187212</v>
+        <v>122187216</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1629,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406102</v>
+        <v>405903</v>
       </c>
       <c r="R10" t="n">
-        <v>7061999</v>
+        <v>7062652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1689,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122187208</v>
+        <v>122187215</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1736,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406081</v>
+        <v>405954</v>
       </c>
       <c r="R11" t="n">
-        <v>7061939</v>
+        <v>7062701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1796,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187211</v>
+        <v>122187210</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1843,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406084</v>
+        <v>406074</v>
       </c>
       <c r="R12" t="n">
-        <v>7061995</v>
+        <v>7061954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187226</v>
+        <v>122187225</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,38 +1915,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406168</v>
+        <v>405849</v>
       </c>
       <c r="R13" t="n">
-        <v>7062607</v>
+        <v>7062237</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,11 +1991,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>riktigt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187213</v>
+        <v>122187209</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406024</v>
+        <v>406088</v>
       </c>
       <c r="R14" t="n">
-        <v>7062128</v>
+        <v>7061950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187214</v>
+        <v>122187211</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405985</v>
+        <v>406084</v>
       </c>
       <c r="R15" t="n">
-        <v>7062528</v>
+        <v>7061995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187210</v>
+        <v>122187228</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406074</v>
+        <v>405889</v>
       </c>
       <c r="R16" t="n">
-        <v>7061954</v>
+        <v>7062449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2338,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187216</v>
+        <v>122187217</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405903</v>
+        <v>405915</v>
       </c>
       <c r="R17" t="n">
-        <v>7062652</v>
+        <v>7061901</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187228</v>
+        <v>122187227</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405889</v>
+        <v>405873</v>
       </c>
       <c r="R18" t="n">
-        <v>7062449</v>
+        <v>7062559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187217</v>
+        <v>122187212</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405915</v>
+        <v>406102</v>
       </c>
       <c r="R19" t="n">
-        <v>7061901</v>
+        <v>7061999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187218</v>
+        <v>122187226</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405949</v>
+        <v>406168</v>
       </c>
       <c r="R20" t="n">
-        <v>7061869</v>
+        <v>7062607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187228</v>
+        <v>122187217</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405889</v>
+        <v>405915</v>
       </c>
       <c r="R16" t="n">
-        <v>7062449</v>
+        <v>7061901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187217</v>
+        <v>122187228</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405915</v>
+        <v>405889</v>
       </c>
       <c r="R17" t="n">
-        <v>7061901</v>
+        <v>7062449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187227</v>
+        <v>122187212</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405873</v>
+        <v>406102</v>
       </c>
       <c r="R18" t="n">
-        <v>7062559</v>
+        <v>7061999</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187212</v>
+        <v>122187227</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406102</v>
+        <v>405873</v>
       </c>
       <c r="R19" t="n">
-        <v>7061999</v>
+        <v>7062559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 57888-2024 artfynd.xlsx
+++ b/artfynd/A 57888-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122187214</v>
+        <v>122187226</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405985</v>
+        <v>406168</v>
       </c>
       <c r="R6" t="n">
-        <v>7062528</v>
+        <v>7062607</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>riktigt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122187218</v>
+        <v>122187216</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405949</v>
+        <v>405903</v>
       </c>
       <c r="R7" t="n">
-        <v>7061869</v>
+        <v>7062652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122187208</v>
+        <v>122187227</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406081</v>
+        <v>405873</v>
       </c>
       <c r="R8" t="n">
-        <v>7061939</v>
+        <v>7062559</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122187213</v>
+        <v>122187225</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,20 +1487,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1508,17 +1508,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406024</v>
+        <v>405849</v>
       </c>
       <c r="R9" t="n">
-        <v>7062128</v>
+        <v>7062237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,11 +1563,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,7 +1589,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122187216</v>
+        <v>122187217</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1622,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405903</v>
+        <v>405915</v>
       </c>
       <c r="R10" t="n">
-        <v>7062652</v>
+        <v>7061901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1669,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,7 +1803,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122187210</v>
+        <v>122187208</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1836,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406074</v>
+        <v>406081</v>
       </c>
       <c r="R12" t="n">
-        <v>7061954</v>
+        <v>7061939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1883,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122187225</v>
+        <v>122187210</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,20 +1922,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1936,29 +1943,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordböle Ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405849</v>
+        <v>406074</v>
       </c>
       <c r="R13" t="n">
-        <v>7062237</v>
+        <v>7061954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,6 +1986,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122187209</v>
+        <v>122187212</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406088</v>
+        <v>406102</v>
       </c>
       <c r="R14" t="n">
-        <v>7061950</v>
+        <v>7061999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122187211</v>
+        <v>122187209</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406084</v>
+        <v>406088</v>
       </c>
       <c r="R15" t="n">
-        <v>7061995</v>
+        <v>7061950</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122187217</v>
+        <v>122187228</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,21 +2247,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405915</v>
+        <v>405889</v>
       </c>
       <c r="R16" t="n">
-        <v>7061901</v>
+        <v>7062449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122187228</v>
+        <v>122187211</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405889</v>
+        <v>406084</v>
       </c>
       <c r="R17" t="n">
-        <v>7062449</v>
+        <v>7061995</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,7 +2445,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122187212</v>
+        <v>122187218</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406102</v>
+        <v>405949</v>
       </c>
       <c r="R18" t="n">
-        <v>7061999</v>
+        <v>7061869</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122187227</v>
+        <v>122187213</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405873</v>
+        <v>406024</v>
       </c>
       <c r="R19" t="n">
-        <v>7062559</v>
+        <v>7062128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122187226</v>
+        <v>122187214</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406168</v>
+        <v>405985</v>
       </c>
       <c r="R20" t="n">
-        <v>7062607</v>
+        <v>7062528</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>riktigt</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
